--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104717_W29.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104717_W29.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>18.4759</v>
+        <v>17.6724</v>
       </c>
       <c r="E2" t="n">
-        <v>16.4942</v>
+        <v>16.352</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9817</v>
+        <v>1.3204</v>
       </c>
       <c r="G2" t="n">
-        <v>10.4219</v>
+        <v>10.4024</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4231</v>
+        <v>1.4167</v>
       </c>
       <c r="I2" t="n">
-        <v>8.998799999999999</v>
+        <v>8.9857</v>
       </c>
       <c r="J2" t="n">
-        <v>11.9787</v>
+        <v>11.9448</v>
       </c>
       <c r="K2" t="n">
-        <v>1.303</v>
+        <v>1.2885</v>
       </c>
       <c r="L2" t="n">
-        <v>10.6757</v>
+        <v>10.6563</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.5568</v>
+        <v>-1.5425</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1201</v>
+        <v>0.1281</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.677</v>
+        <v>-1.6706</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1669</v>
+        <v>1.387</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5367</v>
+        <v>0.4363</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6302</v>
+        <v>0.9507</v>
       </c>
       <c r="V2" t="n">
-        <v>4.7512</v>
+        <v>4.7449</v>
       </c>
       <c r="W2" t="n">
-        <v>3.9788</v>
+        <v>3.9709</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7724</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5767</v>
+        <v>7.5953</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9006</v>
+        <v>6.3093</v>
       </c>
       <c r="F3" t="n">
-        <v>0.676</v>
+        <v>1.2859</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1184</v>
+        <v>6.1189</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5673</v>
+        <v>2.5674</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5511</v>
+        <v>3.5515</v>
       </c>
       <c r="J3" t="n">
-        <v>5.7811</v>
+        <v>5.7707</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5749</v>
+        <v>2.5683</v>
       </c>
       <c r="L3" t="n">
-        <v>3.2062</v>
+        <v>3.2024</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3373</v>
+        <v>0.3482</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0076</v>
+        <v>-0.0009</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3449</v>
+        <v>0.3492</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.633</v>
+        <v>0.3869</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1642</v>
+        <v>0.5874</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7972</v>
+        <v>-0.2005</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3685</v>
+        <v>4.4535</v>
       </c>
       <c r="E4" t="n">
-        <v>7.929</v>
+        <v>7.5165</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.5605</v>
+        <v>-3.063</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1047</v>
+        <v>-0.1086</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4659</v>
+        <v>0.4603</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5705</v>
+        <v>-0.5688</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9241</v>
+        <v>3.9039</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8177</v>
+        <v>2.8021</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1064</v>
+        <v>1.1018</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.0288</v>
+        <v>-4.0125</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.3518</v>
+        <v>-2.3419</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.677</v>
+        <v>-1.6706</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>2.246</v>
+        <v>1.3345</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1174</v>
+        <v>0.7311</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1286</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="W4" t="n">
-        <v>2.8875</v>
+        <v>2.8814</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3745</v>
+        <v>0.3755</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1348</v>
+        <v>1.4759</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5092</v>
+        <v>-1.1004</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0968</v>
+        <v>0.4459</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8145</v>
+        <v>0.9788</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.9113</v>
+        <v>-0.5329</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1094</v>
+        <v>1.3438</v>
       </c>
       <c r="K5" t="n">
-        <v>2.7304</v>
+        <v>0.7929</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.6211</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.2062</v>
+        <v>-0.8979</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.916</v>
+        <v>0.1859</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2902</v>
+        <v>-1.0838</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1359</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1359</v>
+        <v>0.6829</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.186</v>
+        <v>0.107</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0254</v>
+        <v>0.1321</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2115</v>
+        <v>-0.0251</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7724</v>
+        <v>-0.8603</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7724</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7231</v>
+        <v>-0.1477</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5847</v>
+        <v>1.1918</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3078</v>
+        <v>-1.3395</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4393</v>
+        <v>-2.0979</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9752</v>
+        <v>0.8129</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5359</v>
+        <v>-2.9108</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3482</v>
+        <v>1.0992</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7949000000000001</v>
+        <v>2.7234</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5532</v>
+        <v>-1.6242</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9089</v>
+        <v>-3.1971</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1803</v>
+        <v>-1.9105</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0891</v>
+        <v>-1.2866</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6816</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6816</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9795</v>
+        <v>0.0381</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7635</v>
+        <v>0.0926</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2161</v>
+        <v>-0.0545</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8643999999999999</v>
+        <v>0.7739</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8643999999999999</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="7">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1322</v>
+        <v>-0.9689</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8317</v>
+        <v>0.8952</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9639</v>
+        <v>-1.864</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6204</v>
+        <v>-0.6192</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8708</v>
+        <v>0.8702</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4913</v>
+        <v>-1.4895</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0887</v>
+        <v>1.0859</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0887</v>
+        <v>1.0859</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7092</v>
+        <v>-1.7052</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2179</v>
+        <v>-0.2157</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4913</v>
+        <v>-1.4895</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1000,22 +1000,22 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5118</v>
+        <v>-0.3496</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4164</v>
+        <v>-0.3485</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0953</v>
+        <v>-0.0011</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
@@ -1033,37 +1033,37 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5976</v>
+        <v>-1.6965</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5576</v>
+        <v>-2.4424</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9601</v>
+        <v>0.7459</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5523</v>
+        <v>-2.5529</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.5523</v>
+        <v>-2.5529</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.3494</v>
+        <v>-2.3517</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.3494</v>
+        <v>-2.3517</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2029</v>
+        <v>-0.2012</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2029</v>
+        <v>-0.2012</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1078,28 +1078,28 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1823</v>
+        <v>0.0825</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2082</v>
+        <v>-0.0907</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3905</v>
+        <v>0.1732</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7724</v>
+        <v>0.7739</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7724</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1584</v>
+        <v>-2.2055</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9085</v>
+        <v>-1.5541</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.0669</v>
+        <v>-0.6514</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1771</v>
+        <v>-2.1998</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3742</v>
+        <v>-0.4766</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8028999999999999</v>
+        <v>-1.7232</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1465</v>
+        <v>-0.2981</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4441</v>
+        <v>-0.2455</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7023</v>
+        <v>-0.0526</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.3235</v>
+        <v>-1.9017</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.8183</v>
+        <v>-0.231</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.5052</v>
+        <v>-1.6706</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6816</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2719</v>
+        <v>-3.4145</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5903</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>2.0183</v>
+        <v>0.4787</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4644</v>
+        <v>0.3665</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.1121</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3181</v>
+        <v>1.792</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5695</v>
+        <v>1.792</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.8875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>G. PROCIDA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3531</v>
+        <v>-2.4226</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4286</v>
+        <v>0.9106</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9245</v>
+        <v>-3.3332</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.2018</v>
+        <v>-2.629</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4756</v>
+        <v>-1.856</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7263</v>
+        <v>-0.773</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2843</v>
+        <v>0.9273</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2351</v>
+        <v>0.4137</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0493</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9175</v>
+        <v>-3.5563</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2405</v>
+        <v>-2.2697</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.677</v>
+        <v>-1.2866</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.2719</v>
+        <v>1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4078</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3244</v>
+        <v>-0.5448</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4673</v>
+        <v>-0.1745</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1429</v>
+        <v>-0.3703</v>
       </c>
       <c r="V10" t="n">
-        <v>1.7963</v>
+        <v>-0.387</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7963</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. PROCIDA</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2463</v>
+        <v>-2.5978</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2572</v>
+        <v>-0.1498</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5035</v>
+        <v>-2.448</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6361</v>
+        <v>-3.805</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8619</v>
+        <v>-4.1043</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7743</v>
+        <v>0.2992</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9307</v>
+        <v>-0.2211</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4148</v>
+        <v>-2.1793</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5159</v>
+        <v>1.9582</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.5668</v>
+        <v>-3.5839</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.2766</v>
+        <v>-1.9249</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2902</v>
+        <v>-1.659</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3599</v>
+        <v>-0.2464</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8329</v>
+        <v>-0.2442</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.527</v>
+        <v>-0.0022</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3862</v>
+        <v>0.3155</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1594</v>
+        <v>0.3155</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5456</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4449</v>
+        <v>-3.3953</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7962</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6487</v>
+        <v>-4.1671</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.8067</v>
+        <v>-2.1741</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.1076</v>
+        <v>-1.3729</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3009</v>
+        <v>-0.8012</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2127</v>
+        <v>1.1373</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.1766</v>
+        <v>0.4374</v>
       </c>
       <c r="L12" t="n">
-        <v>1.9639</v>
+        <v>0.6998</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.594</v>
+        <v>-3.3114</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.931</v>
+        <v>-1.8103</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.663</v>
+        <v>-1.5011</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1359</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1359</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0929</v>
+        <v>0.7804</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9023</v>
+        <v>0.348</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1906</v>
+        <v>0.4324</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3188</v>
+        <v>-1.3187</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3188</v>
+        <v>1.5628</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.6578</v>
+        <v>-6.8814</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5337</v>
+        <v>-2.711</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.1241</v>
+        <v>-4.1704</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.4365</v>
+        <v>-2.432</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7649</v>
+        <v>-0.764</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.6717</v>
+        <v>-1.668</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4955</v>
+        <v>-0.4995</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6446</v>
+        <v>-0.6485</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1491</v>
+        <v>0.1489</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.941</v>
+        <v>-1.9325</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1203</v>
+        <v>-0.1155</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.8208</v>
+        <v>-1.8169</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.5903</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>0.09719999999999999</v>
+        <v>-0.1323</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2336</v>
+        <v>0.0648</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1365</v>
+        <v>-0.1972</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.7281</v>
+        <v>-2.7237</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.7281</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.733199999999995</v>
+        <v>9.781000000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>27.72460000000001</v>
+        <v>28.5657</v>
       </c>
       <c r="F14" t="n">
-        <v>-18.9913</v>
+        <v>-18.7848</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.652799999999997</v>
+        <v>-1.651300000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.019699999999999</v>
+        <v>-4.0204</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3666</v>
+        <v>2.368999999999998</v>
       </c>
       <c r="J14" t="n">
-        <v>23.9655</v>
+        <v>23.8425</v>
       </c>
       <c r="K14" t="n">
-        <v>6.762799999999999</v>
+        <v>6.687200000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>17.2023</v>
+        <v>17.1551</v>
       </c>
       <c r="M14" t="n">
-        <v>-25.6183</v>
+        <v>-25.494</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.7825</v>
+        <v>-10.7076</v>
       </c>
       <c r="O14" t="n">
-        <v>-14.8359</v>
+        <v>-14.7861</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2717</v>
+        <v>2.276500000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.0875</v>
+        <v>-9.1053</v>
       </c>
       <c r="R14" t="n">
-        <v>11.3592</v>
+        <v>11.3818</v>
       </c>
       <c r="S14" t="n">
-        <v>2.272</v>
+        <v>3.322</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8857000000000003</v>
+        <v>1.9009</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3861</v>
+        <v>1.4208</v>
       </c>
       <c r="V14" t="n">
-        <v>5.842499999999999</v>
+        <v>5.8342</v>
       </c>
       <c r="W14" t="n">
-        <v>11.961</v>
+        <v>11.9277</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.1185</v>
+        <v>-6.0934</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3743</v>
+        <v>3.4114</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1109</v>
+        <v>4.9177</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7366</v>
+        <v>-1.5062</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2754</v>
+        <v>0.278</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6575</v>
+        <v>1.6571</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3821</v>
+        <v>-1.3791</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5048</v>
+        <v>2.4987</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2811</v>
+        <v>2.2753</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2237</v>
+        <v>0.2234</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2294</v>
+        <v>-2.2207</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6237</v>
+        <v>-0.6182</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6058</v>
+        <v>-1.6025</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5533</v>
+        <v>0.5887</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9692</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.416</v>
+        <v>-0.1961</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7398</v>
+        <v>3.3249</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9973</v>
+        <v>6.0525</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.2575</v>
+        <v>-2.7275</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0263</v>
+        <v>3.9867</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0595</v>
+        <v>1.5457</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.0858</v>
+        <v>2.441</v>
       </c>
       <c r="J16" t="n">
-        <v>3.332</v>
+        <v>5.6322</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8335</v>
+        <v>2.006</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4986</v>
+        <v>3.6262</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.3583</v>
+        <v>-1.6455</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.774</v>
+        <v>-0.4603</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.5843</v>
+        <v>-1.1852</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6816</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8175</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1893</v>
+        <v>-0.2764</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2086</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3979</v>
+        <v>0.3441</v>
       </c>
       <c r="V16" t="n">
-        <v>3.2738</v>
+        <v>-0.1578</v>
       </c>
       <c r="W16" t="n">
-        <v>3.5926</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3188</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7291</v>
+        <v>2.6029</v>
       </c>
       <c r="E17" t="n">
-        <v>5.7271</v>
+        <v>5.8316</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.998</v>
+        <v>-3.2288</v>
       </c>
       <c r="G17" t="n">
-        <v>3.9967</v>
+        <v>-1.0394</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5508</v>
+        <v>1.0496</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4459</v>
+        <v>-2.089</v>
       </c>
       <c r="J17" t="n">
-        <v>5.6523</v>
+        <v>3.3005</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0167</v>
+        <v>1.8122</v>
       </c>
       <c r="L17" t="n">
-        <v>3.6356</v>
+        <v>1.4884</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6555</v>
+        <v>-4.34</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4659</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1897</v>
+        <v>-3.5774</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2272</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9087</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.881</v>
+        <v>-0.309</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9717</v>
+        <v>0.0853</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0907</v>
+        <v>-0.3943</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1594</v>
+        <v>3.2684</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1825</v>
+        <v>3.584</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.3419</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="18">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9993</v>
+        <v>1.4439</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5842</v>
+        <v>2.0449</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5848</v>
+        <v>-0.601</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0142</v>
+        <v>-0.0115</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0977</v>
+        <v>0.1002</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1118</v>
+        <v>-0.1117</v>
       </c>
       <c r="J18" t="n">
-        <v>1.168</v>
+        <v>1.1602</v>
       </c>
       <c r="K18" t="n">
-        <v>0.248</v>
+        <v>0.2446</v>
       </c>
       <c r="L18" t="n">
-        <v>0.92</v>
+        <v>0.9156</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1822</v>
+        <v>-1.1717</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1503</v>
+        <v>-0.1444</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0319</v>
+        <v>-1.0273</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5321</v>
+        <v>-0.0893</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6751</v>
+        <v>-0.2047</v>
       </c>
       <c r="U18" t="n">
-        <v>0.143</v>
+        <v>0.1154</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>K. MARTIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3031</v>
+        <v>-0.758</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8943</v>
+        <v>2.7463</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1974</v>
+        <v>-3.5043</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7733</v>
+        <v>0.1434</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4697</v>
+        <v>-1.7866</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6964</v>
+        <v>1.93</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5312</v>
+        <v>4.1125</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8229</v>
+        <v>-0.5935</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7083</v>
+        <v>4.7061</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7579</v>
+        <v>-3.9692</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3532</v>
+        <v>-1.1931</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4047</v>
+        <v>-2.7761</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6816</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6816</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3318</v>
+        <v>-0.5843</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2522</v>
+        <v>-0.2281</v>
       </c>
       <c r="U19" t="n">
-        <v>0.584</v>
+        <v>-0.3562</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.0897</v>
+        <v>-0.5447</v>
       </c>
       <c r="W19" t="n">
-        <v>-2.3847</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.705</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>J. HANDS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4652</v>
+        <v>-0.8096</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.138</v>
+        <v>2.0254</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6728</v>
+        <v>-2.8351</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.341</v>
+        <v>2.715</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8723</v>
+        <v>-0.8302</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4686</v>
+        <v>3.5452</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3023</v>
+        <v>4.7341</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0518</v>
+        <v>0.1616</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3541</v>
+        <v>4.5725</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0387</v>
+        <v>-2.0191</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9242</v>
+        <v>-0.9918</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1145</v>
+        <v>-1.0273</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4544</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8084</v>
+        <v>-0.4564</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1642</v>
+        <v>-0.4324</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6441</v>
+        <v>-0.024</v>
       </c>
       <c r="V20" t="n">
-        <v>0.613</v>
+        <v>-1.2472</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.613</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. MARTIN</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.147</v>
+        <v>-0.9861</v>
       </c>
       <c r="E21" t="n">
-        <v>2.5336</v>
+        <v>0.7527</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.6807</v>
+        <v>-1.7388</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1463</v>
+        <v>1.775</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.789</v>
+        <v>2.4672</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9353</v>
+        <v>-0.6922</v>
       </c>
       <c r="J21" t="n">
-        <v>4.13</v>
+        <v>3.5204</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5867</v>
+        <v>2.8129</v>
       </c>
       <c r="L21" t="n">
-        <v>4.7167</v>
+        <v>0.7075</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.9837</v>
+        <v>-1.7453</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2022</v>
+        <v>-0.3457</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.7814</v>
+        <v>-1.3997</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2272</v>
+        <v>0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3631</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9749</v>
+        <v>-0.3483</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4604</v>
+        <v>-0.3743</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5145</v>
+        <v>0.0261</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5456</v>
+        <v>-3.0958</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-2.3933</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5456</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="22">
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3557</v>
+        <v>-1.1066</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6187</v>
+        <v>0.7355</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9744</v>
+        <v>-1.842</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1285</v>
+        <v>1.1304</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3569</v>
+        <v>0.3587</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7716</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7575</v>
+        <v>0.7564</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0864</v>
+        <v>0.0862</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6711</v>
+        <v>0.6703</v>
       </c>
       <c r="M22" t="n">
-        <v>0.371</v>
+        <v>0.374</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2705</v>
+        <v>0.2725</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1005</v>
+        <v>0.1014</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2170,28 +2170,28 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3017</v>
+        <v>-0.058</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1388</v>
+        <v>-0.021</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1629</v>
+        <v>-0.037</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. HANDS</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3752</v>
+        <v>-1.2177</v>
       </c>
       <c r="E23" t="n">
-        <v>1.573</v>
+        <v>-1.4972</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9483</v>
+        <v>0.2795</v>
       </c>
       <c r="G23" t="n">
-        <v>2.716</v>
+        <v>-2.3368</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8317</v>
+        <v>-0.8679</v>
       </c>
       <c r="I23" t="n">
-        <v>3.5477</v>
+        <v>-1.4689</v>
       </c>
       <c r="J23" t="n">
-        <v>4.7472</v>
+        <v>-1.3042</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1676</v>
+        <v>0.0517</v>
       </c>
       <c r="L23" t="n">
-        <v>4.5796</v>
+        <v>-1.3559</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0312</v>
+        <v>-1.0326</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9994</v>
+        <v>-0.9196</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0319</v>
+        <v>-0.113</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8175</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2719</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.023</v>
+        <v>0.0476</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9023</v>
+        <v>-0.193</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1207</v>
+        <v>0.2407</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2507</v>
+        <v>0.6162</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2507</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4932</v>
+        <v>-1.3321</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.915</v>
+        <v>-0.9175</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5782</v>
+        <v>-0.4146</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0009</v>
+        <v>-0.9991</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.13</v>
+        <v>-1.1288</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1292</v>
+        <v>0.1297</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5679</v>
+        <v>-0.569</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7543</v>
+        <v>-0.7552</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1864</v>
+        <v>0.1862</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4329</v>
+        <v>-0.4301</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3757</v>
+        <v>-0.3736</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0573</v>
+        <v>-0.0565</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4007</v>
+        <v>-0.2451</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.347</v>
+        <v>-0.3485</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0537</v>
+        <v>0.1035</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3188</v>
+        <v>-0.3155</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3188</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.7804</v>
+        <v>-5.7203</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.4573</v>
+        <v>-1.359</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.3231</v>
+        <v>-4.3613</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.7417</v>
+        <v>-1.7354</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5477</v>
+        <v>1.5504</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.2894</v>
+        <v>-3.2858</v>
       </c>
       <c r="J25" t="n">
-        <v>2.1837</v>
+        <v>2.1744</v>
       </c>
       <c r="K25" t="n">
-        <v>2.4194</v>
+        <v>2.4132</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.2357</v>
+        <v>-0.2388</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.9254</v>
+        <v>-3.9098</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.8716</v>
+        <v>-0.8628</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.0537</v>
+        <v>-3.0471</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.0447</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3572</v>
+        <v>-0.302</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2332</v>
+        <v>-0.1189</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.124</v>
+        <v>-0.183</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.6559</v>
+        <v>-7.5882</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.5375</v>
+        <v>-2.5481</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.1184</v>
+        <v>-5.0401</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.2593</v>
+        <v>-2.2548</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0969</v>
+        <v>-0.095</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.1623</v>
+        <v>-2.1597</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.5182</v>
+        <v>-0.5223</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1961</v>
+        <v>0.1929</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.7143</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.741</v>
+        <v>-1.7325</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.2931</v>
+        <v>-0.2879</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.448</v>
+        <v>-1.4446</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.8175</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3054</v>
+        <v>-0.244</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2526</v>
+        <v>0.2505</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.4945</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.2738</v>
+        <v>-3.2684</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.2738</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-8.7332</v>
+        <v>-8.735499999999998</v>
       </c>
       <c r="E27" t="n">
-        <v>18.9913</v>
+        <v>18.7848</v>
       </c>
       <c r="F27" t="n">
-        <v>-27.7246</v>
+        <v>-27.5202</v>
       </c>
       <c r="G27" t="n">
-        <v>1.6528</v>
+        <v>1.651499999999998</v>
       </c>
       <c r="H27" t="n">
-        <v>4.019900000000001</v>
+        <v>4.0204</v>
       </c>
       <c r="I27" t="n">
-        <v>-2.366700000000001</v>
+        <v>-2.368799999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>25.6183</v>
+        <v>25.49389999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>10.7825</v>
+        <v>10.7079</v>
       </c>
       <c r="L27" t="n">
-        <v>14.8359</v>
+        <v>14.7863</v>
       </c>
       <c r="M27" t="n">
-        <v>-23.9652</v>
+        <v>-23.8425</v>
       </c>
       <c r="N27" t="n">
-        <v>-6.7628</v>
+        <v>-6.687499999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>-17.2027</v>
+        <v>-17.1553</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.2718</v>
+        <v>-2.2764</v>
       </c>
       <c r="Q27" t="n">
-        <v>-11.3593</v>
+        <v>-11.3817</v>
       </c>
       <c r="R27" t="n">
-        <v>9.087499999999999</v>
+        <v>9.105399999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.2718</v>
+        <v>-2.2765</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.3861</v>
+        <v>-1.4208</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.8859</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>-5.8424</v>
+        <v>-5.834200000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>6.118599999999999</v>
+        <v>6.093299999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>-11.961</v>
+        <v>-11.9274</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104717_W29.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104717_W29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.0934</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104717_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-11.9274</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
